--- a/results/04_final_refined_daily_hydroclimate_data/702/Max_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/702/Max_Temperature_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -414,7 +414,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>27.8</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -470,7 +470,7 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>27.3</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -483,8 +483,8 @@
       <c r="C7">
         <v>6</v>
       </c>
-      <c r="D7" t="s">
-        <v>4</v>
+      <c r="D7">
+        <v>27.3</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -497,8 +497,8 @@
       <c r="C8">
         <v>7</v>
       </c>
-      <c r="D8" t="s">
-        <v>4</v>
+      <c r="D8">
+        <v>25.9</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -525,8 +525,8 @@
       <c r="C10">
         <v>9</v>
       </c>
-      <c r="D10" t="s">
-        <v>4</v>
+      <c r="D10">
+        <v>23.6</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -596,7 +596,7 @@
         <v>14</v>
       </c>
       <c r="D15">
-        <v>24.5</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -623,8 +623,8 @@
       <c r="C17">
         <v>16</v>
       </c>
-      <c r="D17" t="s">
-        <v>4</v>
+      <c r="D17">
+        <v>25.9</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -651,8 +651,8 @@
       <c r="C19">
         <v>18</v>
       </c>
-      <c r="D19" t="s">
-        <v>4</v>
+      <c r="D19">
+        <v>25.7</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -680,7 +680,7 @@
         <v>20</v>
       </c>
       <c r="D21">
-        <v>28.3</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -764,7 +764,7 @@
         <v>26</v>
       </c>
       <c r="D27">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -778,7 +778,7 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -792,7 +792,7 @@
         <v>28</v>
       </c>
       <c r="D29">
-        <v>28.4</v>
+        <v>28.94</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -834,7 +834,7 @@
         <v>2</v>
       </c>
       <c r="D32">
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -848,7 +848,7 @@
         <v>3</v>
       </c>
       <c r="D33">
-        <v>24.9</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -889,8 +889,8 @@
       <c r="C36">
         <v>6</v>
       </c>
-      <c r="D36" t="s">
-        <v>4</v>
+      <c r="D36">
+        <v>23.4</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -917,8 +917,8 @@
       <c r="C38">
         <v>8</v>
       </c>
-      <c r="D38" t="s">
-        <v>4</v>
+      <c r="D38">
+        <v>24.6</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -946,7 +946,7 @@
         <v>10</v>
       </c>
       <c r="D40">
-        <v>27.5</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -973,8 +973,8 @@
       <c r="C42">
         <v>12</v>
       </c>
-      <c r="D42" t="s">
-        <v>4</v>
+      <c r="D42">
+        <v>25.6</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -987,8 +987,8 @@
       <c r="C43">
         <v>13</v>
       </c>
-      <c r="D43" t="s">
-        <v>4</v>
+      <c r="D43">
+        <v>27.1</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1002,7 +1002,7 @@
         <v>14</v>
       </c>
       <c r="D44">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1015,8 +1015,8 @@
       <c r="C45">
         <v>15</v>
       </c>
-      <c r="D45" t="s">
-        <v>4</v>
+      <c r="D45">
+        <v>25.8</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1029,8 +1029,8 @@
       <c r="C46">
         <v>16</v>
       </c>
-      <c r="D46" t="s">
-        <v>4</v>
+      <c r="D46">
+        <v>23.1</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1044,7 +1044,7 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1085,8 +1085,8 @@
       <c r="C50">
         <v>20</v>
       </c>
-      <c r="D50" t="s">
-        <v>4</v>
+      <c r="D50">
+        <v>23.7</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1170,7 +1170,7 @@
         <v>26</v>
       </c>
       <c r="D56">
-        <v>25.9</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1184,7 +1184,7 @@
         <v>27</v>
       </c>
       <c r="D57">
-        <v>26.1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1211,8 +1211,8 @@
       <c r="C59">
         <v>29</v>
       </c>
-      <c r="D59">
-        <v>26.9</v>
+      <c r="D59" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1226,7 +1226,7 @@
         <v>30</v>
       </c>
       <c r="D60">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
     </row>
   </sheetData>

--- a/results/04_final_refined_daily_hydroclimate_data/702/Max_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/702/Max_Temperature_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Year</t>
   </si>
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t>Max_Temperature</t>
-  </si>
-  <si>
-    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -512,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="D9">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -526,7 +523,7 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -652,7 +649,7 @@
         <v>18</v>
       </c>
       <c r="D19">
-        <v>25.7</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -792,7 +789,7 @@
         <v>28</v>
       </c>
       <c r="D29">
-        <v>28.94</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -974,7 +971,7 @@
         <v>12</v>
       </c>
       <c r="D42">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -988,7 +985,7 @@
         <v>13</v>
       </c>
       <c r="D43">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1086,7 +1083,7 @@
         <v>20</v>
       </c>
       <c r="D50">
-        <v>23.7</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1099,8 +1096,8 @@
       <c r="C51">
         <v>21</v>
       </c>
-      <c r="D51" t="s">
-        <v>4</v>
+      <c r="D51">
+        <v>25.6</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1127,8 +1124,8 @@
       <c r="C53">
         <v>23</v>
       </c>
-      <c r="D53" t="s">
-        <v>4</v>
+      <c r="D53">
+        <v>21.7</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1170,7 +1167,7 @@
         <v>26</v>
       </c>
       <c r="D56">
-        <v>25.1</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1211,8 +1208,8 @@
       <c r="C59">
         <v>29</v>
       </c>
-      <c r="D59" t="s">
-        <v>4</v>
+      <c r="D59">
+        <v>26.9</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1226,7 +1223,7 @@
         <v>30</v>
       </c>
       <c r="D60">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
     </row>
   </sheetData>

--- a/results/04_final_refined_daily_hydroclimate_data/702/Max_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/702/Max_Temperature_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -26,6 +26,9 @@
   </si>
   <si>
     <t>Max_Temperature</t>
+  </si>
+  <si>
+    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -761,7 +764,7 @@
         <v>26</v>
       </c>
       <c r="D27">
-        <v>26.9</v>
+        <v>26.92</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1097,7 +1100,7 @@
         <v>21</v>
       </c>
       <c r="D51">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1124,8 +1127,8 @@
       <c r="C53">
         <v>23</v>
       </c>
-      <c r="D53">
-        <v>21.7</v>
+      <c r="D53" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/702/Max_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/702/Max_Temperature_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Year</t>
   </si>
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t>Max_Temperature</t>
-  </si>
-  <si>
-    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -764,7 +761,7 @@
         <v>26</v>
       </c>
       <c r="D27">
-        <v>26.92</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1100,7 +1097,7 @@
         <v>21</v>
       </c>
       <c r="D51">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1127,8 +1124,8 @@
       <c r="C53">
         <v>23</v>
       </c>
-      <c r="D53" t="s">
-        <v>4</v>
+      <c r="D53">
+        <v>21.7</v>
       </c>
     </row>
     <row r="54" spans="1:4">
